--- a/Meilenstein 2/Lieferanten/JB-Licht GmbH/JB-Licht GmbH_Warranty_Inquiry.xlsx
+++ b/Meilenstein 2/Lieferanten/JB-Licht GmbH/JB-Licht GmbH_Warranty_Inquiry.xlsx
@@ -3,20 +3,21 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Warranty_Data_Collection" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Warranty_Data_Entry" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,22 +28,48 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E7D32"/>
+        <bgColor rgb="FF2E7D32"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F8E9"/>
+        <bgColor rgb="FFF1F8E9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -50,56 +77,86 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCBD5E0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCBD5E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCBD5E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCBD5E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF003399"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF003399"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF003399"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF003399"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-  </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -172,18 +229,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabelle_EN_JB_Licht_GmbH" displayName="Tabelle_EN_JB_Licht_GmbH" ref="A1:I3" headerRowCount="1">
-  <autoFilter ref="A1:I3"/>
-  <tableColumns count="9">
-    <tableColumn id="1" name="Supplier ID"/>
-    <tableColumn id="2" name="Supplier Name"/>
-    <tableColumn id="3" name="SKU / Article Number"/>
-    <tableColumn id="4" name="Product Description"/>
-    <tableColumn id="5" name="Brand (short form for label - e.g. Miele)"/>
-    <tableColumn id="6" name="Model Identifier (for Label)"/>
-    <tableColumn id="7" name="Manufacturer Warranty (in years)"/>
-    <tableColumn id="8" name="Link to Warranty Conditions (URL starting with https://)"/>
-    <tableColumn id="9" name="Warranty is free of charge &amp; covers entire product? (Yes/No)"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_JB_Licht_GmbH" displayName="Table_JB_Licht_GmbH" ref="A1:G3" headerRowCount="1">
+  <autoFilter ref="A1:G3"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="EAN / GTIN (Barcode)"/>
+    <tableColumn id="2" name="Supplier SKU / Article Number"/>
+    <tableColumn id="3" name="Brand"/>
+    <tableColumn id="4" name="Model identifier"/>
+    <tableColumn id="5" name="Warranty period in years (XX)"/>
+    <tableColumn id="6" name="Link to the warranty conditions"/>
+    <tableColumn id="7" name="Confirmation 'Free &amp; full warranty' (Yes/No)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -200,39 +255,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -264,10 +319,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -299,7 +353,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -311,142 +364,166 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -456,134 +533,242 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="15" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
-    <col width="17" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
-    <col width="24" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
-    <col width="42" bestFit="1" customWidth="1" style="1" min="4" max="4"/>
-    <col width="44" bestFit="1" customWidth="1" style="1" min="5" max="5"/>
-    <col width="35" customWidth="1" style="1" min="6" max="6"/>
-    <col width="35" customWidth="1" style="1" min="7" max="8"/>
-    <col width="59" customWidth="1" min="8" max="8"/>
-    <col width="63" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
+    <col width="77.5703125" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Field Attribute / Column</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Example Entry for a Sample Product</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Justification / Legal Basis (Why is this required?)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="39.95" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>EAN / GTIN (Barcode)</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>4895251607063</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Used for unique and automated product assignment in the SBS database. Without EAN, automated import is not possible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="39.95" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Supplier SKU / Article Number</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>EF BD-5.1-S1</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Used as a backup key for assignment and facilitates unique identification in case of queries or data errors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="39.95" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>EcoFlow</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Mandatory legal field ('Brand/Trademark') according to Implementing Regulation (EU) 2025/1960. Printed directly on the warranty label.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="39.95" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Model identifier</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>PowerOcean LFP Batterie (5 kWh)</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Mandatory legal field ('Model identifier') according to Implementing Regulation (EU) 2025/1960. Must exactly match the markings on the product.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="39.95" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Warranty period in years (XX)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Mandatory legal field according to Implementing Regulation (EU) 2025/1960. Determines the printed warranty period (years &gt; 2) on the EU label.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="69.75" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Link to the warranty conditions</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>https://enterprise-service-eu-cdn.ecoflow.com/enterprise/documentation/1719480779438/20240627EcoFlow%20Warranty%20Policy%20for%20Home%20Solar%20Battery%20Solutions%20in%20Europe%20B%20V1.3-EN.pdf</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Mandatory legal requirement under § 9a Abs 3 KSchG / Directive (EU) 2024/825. Warranty conditions must be provided to the consumer on a durable medium (e.g. downloadable PDF link).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="39.95" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Confirmation 'Free &amp; full warranty' (Yes/No)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Legal safeguard for SBS. The green EU warranty label may only be used for free warranties covering the entire product (avoidance of warning letters).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="21.95" customHeight="1"/>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="4"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Supplier ID</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Supplier Name</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>SKU / Article Number</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Product Description</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Brand (short form for label - e.g. Miele)</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Model Identifier (for Label)</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Manufacturer Warranty (in years)</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Link to Warranty Conditions (URL starting with https://)</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>Warranty is free of charge &amp; covers entire product? (Yes/No)</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EAN / GTIN (Barcode)</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Supplier SKU / Article Number</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Model identifier</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Warranty period in years (XX)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Link to the warranty conditions</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Confirmation 'Free &amp; full warranty' (Yes/No)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>310678</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>JB-Licht GmbH</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>LENETI20106</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>* 602016  OVALARMATUR 60 WATT SCHWARZ</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="n"/>
-      <c r="F2" s="6" t="n"/>
-      <c r="G2" s="7" t="n"/>
-      <c r="H2" s="6" t="n"/>
-      <c r="I2" s="7" t="n"/>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>310678</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>JB-Licht GmbH</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>LENETI40606</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>* 604065  RUNDARMATUR 100 WATT SCHWARZ</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="7" t="n"/>
-      <c r="H3" s="6" t="n"/>
-      <c r="I3" s="7" t="n"/>
+      <c r="F3" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="E2:E3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Brand Name" prompt="Please enter the short brand name to be shown on the label (e.g. &quot;Miele&quot; instead of &quot;Miele GmbH&quot;)."/>
-    <dataValidation sqref="F2:F3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Model Identifier" prompt="Please enter the exact manufacturer model code (e.g. &quot;WXD160&quot;)."/>
-    <dataValidation sqref="G2:G3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Value" error="Please enter a whole number greater than 2 (e.g. 3, 5, 10)." promptTitle="Manufacturer Warranty" prompt="Please enter the warranty period in years as a whole number only (e.g., 3, 5, 10). Do not write &quot;years&quot; or &quot;y&quot;." type="whole" operator="greaterThan">
+    <dataValidation sqref="C2:C3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Brand" prompt="Please enter the short brand name to be shown on the label (e.g. &quot;Miele&quot; instead of &quot;Miele GmbH&quot;)."/>
+    <dataValidation sqref="D2:D3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Model Identifier" prompt="Please enter the exact manufacturer model code (e.g. &quot;WXD160&quot;)."/>
+    <dataValidation sqref="E2:E3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Value" error="Please enter a whole number greater than 2 (e.g. 3, 5, 10)." promptTitle="Manufacturer Warranty" prompt="Please enter the warranty period in years as a whole number only (e.g., 3, 5, 10). Do not write &quot;years&quot; or &quot;y&quot;." type="whole" operator="greaterThan">
       <formula1>2</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Link to Warranty Conditions" prompt="Please enter the direct URL link to the warranty conditions on your website (e.g., https://www.manufacturer.com/warranty). Do not write free text like &quot;in the box&quot;."/>
-    <dataValidation sqref="I2:I3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Selection" error="Invalid selection. Please select Yes or No from the dropdown menu." promptTitle="Warranty Confirmation" prompt="Please select &quot;Yes&quot; or &quot;No&quot; from the dropdown menu." type="list">
+    <dataValidation sqref="F2:F3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Link to Warranty Conditions" prompt="Please enter the direct URL link to the warranty conditions on your website (e.g., https://www.manufacturer.com/warranty). Do not write free text like &quot;in the box&quot;."/>
+    <dataValidation sqref="G2:G3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Selection" error="Invalid selection. Please select Yes or No from the dropdown menu." promptTitle="Warranty Confirmation" prompt="Please select &quot;Yes&quot; or &quot;No&quot; from the dropdown menu." type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.787401575" bottom="0.787401575" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
